--- a/Lab B/Lab11/L11_part_2.xlsx
+++ b/Lab B/Lab11/L11_part_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\School\openu-courses\Lab B\Lab11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97FA3B85-2D5B-4E8B-BE9D-791FF64EFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B616617-E904-4FA0-8190-82BA2AD98157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16D01DD9-B812-4753-A392-552EDD7F64AD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{16D01DD9-B812-4753-A392-552EDD7F64AD}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -56,7 +53,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -102,9 +99,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -142,7 +139,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -248,7 +245,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -390,7 +387,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -398,511 +395,512 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AADC06AA-FB7D-4BEF-A219-59AF6E7C1E90}">
-  <dimension ref="J3:L44"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="11" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="K3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="L3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="B2">
         <v>1.2</v>
       </c>
-      <c r="L4">
-        <f>K4/10</f>
+      <c r="C2">
+        <f>B2/10</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J5">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="K5">
+      <c r="B3">
         <v>1.2</v>
       </c>
-      <c r="L5">
-        <f t="shared" ref="L5:L44" si="0">K5/10</f>
+      <c r="C3">
+        <f t="shared" ref="C3:C42" si="0">B3/10</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>4</v>
       </c>
-      <c r="K6">
+      <c r="B4">
         <v>1.2</v>
       </c>
-      <c r="L6">
+      <c r="C4">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J7">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>6</v>
       </c>
-      <c r="K7">
+      <c r="B5">
         <v>1.2</v>
       </c>
-      <c r="L7">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J8">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>8</v>
       </c>
-      <c r="K8">
+      <c r="B6">
         <v>1.2</v>
       </c>
-      <c r="L8">
+      <c r="C6">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J9">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>10</v>
       </c>
-      <c r="K9">
+      <c r="B7">
         <v>1.2</v>
       </c>
-      <c r="L9">
+      <c r="C7">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J10">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>12</v>
       </c>
-      <c r="K10">
+      <c r="B8">
         <v>1.25</v>
       </c>
-      <c r="L10">
+      <c r="C8">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
     </row>
-    <row r="11" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J11">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>14</v>
       </c>
-      <c r="K11">
+      <c r="B9">
         <v>1.4</v>
       </c>
-      <c r="L11">
+      <c r="C9">
         <f t="shared" si="0"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="12" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J12">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>16</v>
       </c>
-      <c r="K12">
+      <c r="B10">
         <v>1.5</v>
       </c>
-      <c r="L12">
+      <c r="C10">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J13">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>18</v>
       </c>
-      <c r="K13">
+      <c r="B11">
         <v>1.6</v>
       </c>
-      <c r="L13">
+      <c r="C11">
         <f t="shared" si="0"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="14" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J14">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>20</v>
       </c>
-      <c r="K14">
+      <c r="B12">
         <v>1.4</v>
       </c>
-      <c r="L14">
+      <c r="C12">
         <f t="shared" si="0"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="15" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>22</v>
       </c>
-      <c r="K15">
+      <c r="B13">
         <v>1.3</v>
       </c>
-      <c r="L15">
+      <c r="C13">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="16" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J16">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>24</v>
       </c>
-      <c r="K16">
+      <c r="B14">
         <v>1.3</v>
       </c>
-      <c r="L16">
+      <c r="C14">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J17">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>26</v>
       </c>
-      <c r="K17">
+      <c r="B15">
         <v>1.5</v>
       </c>
-      <c r="L17">
+      <c r="C15">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="18" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J18">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>28</v>
       </c>
-      <c r="K18">
+      <c r="B16">
         <v>1.8</v>
       </c>
-      <c r="L18">
+      <c r="C16">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J19">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>30</v>
       </c>
-      <c r="K19">
+      <c r="B17">
         <v>1.8</v>
       </c>
-      <c r="L19">
+      <c r="C17">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="20" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J20">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>32</v>
       </c>
-      <c r="K20">
+      <c r="B18">
         <v>1.5</v>
       </c>
-      <c r="L20">
+      <c r="C18">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J21">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>34</v>
       </c>
-      <c r="K21">
+      <c r="B19">
         <v>1.3</v>
       </c>
-      <c r="L21">
+      <c r="C19">
         <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="22" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J22">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>36</v>
       </c>
-      <c r="K22">
+      <c r="B20">
         <v>1.4</v>
       </c>
-      <c r="L22">
+      <c r="C20">
         <f t="shared" si="0"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J23">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>38</v>
       </c>
-      <c r="K23">
+      <c r="B21">
         <v>1.8</v>
       </c>
-      <c r="L23">
+      <c r="C21">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="24" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J24">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>40</v>
       </c>
-      <c r="K24">
+      <c r="B22">
         <v>2.1</v>
       </c>
-      <c r="L24">
+      <c r="C22">
         <f t="shared" si="0"/>
         <v>0.21000000000000002</v>
       </c>
     </row>
-    <row r="25" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>42</v>
       </c>
-      <c r="K25">
+      <c r="B23">
         <v>2</v>
       </c>
-      <c r="L25">
+      <c r="C23">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="26" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J26">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>44</v>
       </c>
-      <c r="K26">
+      <c r="B24">
         <v>1.6</v>
       </c>
-      <c r="L26">
+      <c r="C24">
         <f t="shared" si="0"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J27">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>46</v>
       </c>
-      <c r="K27">
+      <c r="B25">
         <v>1.4</v>
       </c>
-      <c r="L27">
+      <c r="C25">
         <f t="shared" si="0"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J28">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>48</v>
       </c>
-      <c r="K28">
+      <c r="B26">
         <v>1.4</v>
       </c>
-      <c r="L28">
+      <c r="C26">
         <f t="shared" si="0"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J29">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>50</v>
       </c>
-      <c r="K29">
+      <c r="B27">
         <v>1.8</v>
       </c>
-      <c r="L29">
+      <c r="C27">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="30" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J30">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>52</v>
       </c>
-      <c r="K30">
+      <c r="B28">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L30">
+      <c r="C28">
         <f t="shared" si="0"/>
         <v>0.22000000000000003</v>
       </c>
     </row>
-    <row r="31" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J31">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>54</v>
       </c>
-      <c r="K31">
+      <c r="B29">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L31">
+      <c r="C29">
         <f t="shared" si="0"/>
         <v>0.22000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J32">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>56</v>
       </c>
-      <c r="K32">
+      <c r="B30">
         <v>1.9</v>
       </c>
-      <c r="L32">
+      <c r="C30">
         <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J33">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>58</v>
       </c>
-      <c r="K33">
+      <c r="B31">
         <v>1.6</v>
       </c>
-      <c r="L33">
+      <c r="C31">
         <f t="shared" si="0"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J34">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>60</v>
       </c>
-      <c r="K34">
+      <c r="B32">
         <v>1.5</v>
       </c>
-      <c r="L34">
+      <c r="C32">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>62</v>
       </c>
-      <c r="K35">
+      <c r="B33">
         <v>1.6</v>
       </c>
-      <c r="L35">
+      <c r="C33">
         <f t="shared" si="0"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J36">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>64</v>
       </c>
-      <c r="K36">
+      <c r="B34">
         <v>2</v>
       </c>
-      <c r="L36">
+      <c r="C34">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J37">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>66</v>
       </c>
-      <c r="K37">
+      <c r="B35">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L37">
+      <c r="C35">
         <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
     </row>
-    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J38">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>68</v>
       </c>
-      <c r="K38">
+      <c r="B36">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L38">
+      <c r="C36">
         <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
     </row>
-    <row r="39" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J39">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>70</v>
       </c>
-      <c r="K39">
+      <c r="B37">
         <v>2</v>
       </c>
-      <c r="L39">
+      <c r="C37">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="40" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J40">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>72</v>
       </c>
-      <c r="K40">
+      <c r="B38">
         <v>1.8</v>
       </c>
-      <c r="L40">
+      <c r="C38">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J41">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>74</v>
       </c>
-      <c r="K41">
+      <c r="B39">
         <v>1.8</v>
       </c>
-      <c r="L41">
+      <c r="C39">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="42" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J42">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>76</v>
       </c>
-      <c r="K42">
+      <c r="B40">
         <v>2.1</v>
       </c>
-      <c r="L42">
+      <c r="C40">
         <f t="shared" si="0"/>
         <v>0.21000000000000002</v>
       </c>
     </row>
-    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J43">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>78</v>
       </c>
-      <c r="K43">
+      <c r="B41">
         <v>2.4</v>
       </c>
-      <c r="L43">
+      <c r="C41">
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J44">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>80</v>
       </c>
-      <c r="K44">
+      <c r="B42">
         <v>2.4</v>
       </c>
-      <c r="L44">
+      <c r="C42">
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>

--- a/Lab B/Lab11/L11_part_2.xlsx
+++ b/Lab B/Lab11/L11_part_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\School\openu-courses\Lab B\Lab11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B616617-E904-4FA0-8190-82BA2AD98157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA8F53E-C954-4AFA-87A8-2AFFB8806DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{16D01DD9-B812-4753-A392-552EDD7F64AD}"/>
+    <workbookView xWindow="-28920" yWindow="2655" windowWidth="29040" windowHeight="16440" xr2:uid="{16D01DD9-B812-4753-A392-552EDD7F64AD}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -96,6 +96,1306 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>4.5V</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="he-IL" baseline="0"/>
+              <a:t>מתח הסקה</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>גיליון1!$A$2:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>גיליון1!$C$2:$C$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.21000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.13999999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.22000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.22000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.22999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.22999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.21000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-05F1-4416-A5C2-BDFE61CC6567}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1571808240"/>
+        <c:axId val="1302539216"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1571808240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>[V] </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="he-IL"/>
+                  <a:t>מתח</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1302539216"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1302539216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>[mA] </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="he-IL"/>
+                  <a:t>זרם</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1571808240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>501015</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>139065</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>81915</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3EBCD72-27D9-7C61-B3EF-C37E22D48E3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -907,5 +2207,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>